--- a/data.xlsx
+++ b/data.xlsx
@@ -11,12 +11,1062 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="432">
   <si>
     <t>File Name</t>
   </si>
   <si>
     <t>File URL</t>
+  </si>
+  <si>
+    <t>WhatsApp Image 2026-02-24 at 11.52.28 AM.jpeg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1tDBI-1cw98kN8Wqt6zU66EMXcnTNkN39/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0140.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xeZZSmET3lZo3DD1ZvD1m6iHEPjEik4o/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0105.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1eR3ykmFPQK_zS9Wl1BNQ3uIftW-lxuoy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0030.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17TwrmwvMn_p8g898sNpYPKjJSMG0wf75/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0026.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RU7TbWHfrI_2nNIrsuyloZzjbl67sKLs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0025.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DnukaIy01QLY7QUWTmDLctNvS7KM-Flm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0024.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oSwCRT8kxVvAt8tmrj-r1gK1COuBn9wF/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0023.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vNiDxMKvWZXKuI3YeUqC8JjWn2Sp4x1N/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0022.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K6Iwo6iL_CaFSNnAQ_SAFqUUNB2cXApx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0020.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17QbfhmvjMoCgl20_jVTRULsdPm-DZW3i/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0019.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QKb5jsuNs63rF6Hys7OkZwD8MOFk9wA9/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0017.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SEbt7MGG3Bn1RuWqye2r6Rf5PIGNYC27/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0016.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JS49p4kDVobwizM9I14kEjLBrJ4C8pSx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0015.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Gj7oVUTSipx9DteoOMs020nkzq03nvnt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0014.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NHpzwcmwJOqzziyrKOeiBHw1BnYsSgHr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260222-WA0012.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G2ndfBunOvMTiGbRZZsmsMJrDAbZfDKv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0115.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Id_tyOx2Z1xuQwmrUPc50YD7QYGGn8Hm/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0114.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FOTVw5JN7CMTxnVfqci8Pn0v4NbEn9Ss/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0113.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12M4gZ7i_9EmBbRY4scH9SLhq5FSMwJ85/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0112.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13mANtA9Vf14pO4TiqyOEUpYI-1uFqvuu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0111.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rRjhTN5yAJ26AEPZakfazPTQ_Zjvm79B/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0110.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lVM1aacCCKzAmO_E_Jdx-f7gWJq-Afvk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0109.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11-yH_Wz9Qv872zpm7QTgSknkeElc_QsC/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0108.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1i76xU8an3UF9EEpM5O3aYrR7l_WVRBXG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0107.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1p7ljJkuiDb8aCSFcJXc5xfu4nJtRuJKz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0106.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_VuaV7CYS7E4e3_zBSOaVg4kLsIS4uVH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0105.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Q1LWjGTTYRhMPsCkfMkebP9HVt6N-9a3/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0104.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UXxvYTIHbE1yGgLswlPJ4CHntJs_3qlY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0103.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GyxQN2nemgc9VXIxExpPkNYTnHcvmUVJ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0102.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1idyfmKwklCEiGCciDn2MTR_lRNyuUGBX/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0101.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1b9LyeWVNcUVdcr4HImP_lMq895YsE12Z/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0100.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AvzEHiGvx9W0CTEQ07dcfeHyOxFIqNDg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0099.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Uli2la9dNWpacweb_2wrTVyMHmJj4nm7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0098.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1inlWrdGh2lmCDBuhTGxJlkfZK2yLfpVk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0097.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1i5Y_EgQBuPB7QDYJGRA-bMqfTBPHMKoP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0096.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1a40X0p0eAFynlUBklk__9mogIJb6GgNI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0095.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GnY5s6r9GsCky9hoizp-hxaSYsrUCOtJ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0094.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/198GQLZNfJwLUQQW4vJEt441ivi3s-733/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0093.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EvvB8YAPxyfyQI3_Hwj-y_4lHj8ryCKb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0092.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zmo71BMwLIYUDNUVNM10w-CBzMzQsivR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0091.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16jj3-QHjCk9kwR93iaxG-gyDDRQ6DILD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0090.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TbitjTflNzB8O1bF1ppguxv2btI36juz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0089.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/173Hd-cgrzFC7Nw5uY7BbGLcWoCW-Etvj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0088.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18pbqi99pF8_0mu6sZ7LKVbpT27X2Z8Yg/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0087.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11JS_ymQmeDltJGylKpKfxB7FqDalyzsj/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0086.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SzRgqQrhmo4hoc2baxlKfL8ZRpnXaiGp/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0085.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xzFg7JUCR8lFSZftATA_u1i3QA4HTSBO/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0084.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16fz0PnX_KbtEDXVwVhfua0BviuEVaPmD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0083.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x5476HQeCazuRUbSsd7U7Ix1Df15DRTQ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0082.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15mVodNDW_9rlyQsKz3dGPK2rW97qBBOK/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0081.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18Yz1neSYsKnabvP-EZMSTKeQj8yByWz7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0080.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xOdM26F0gwPlthtDtpkmw4Vr8HyGjIYE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0078.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Zb1UvnvJc8VbBamBa1uOGDMKhUT-HP56/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0077.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qMbV3hhhlOwpybOxNdKeOagucNcgX86k/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0076.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MxvcMPd3w0IS0BYxmpIxCoX4__j7W7Eb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0075.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17BhNmWBvJz322w0wBZaU3nkB_g3yjmi0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0074.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RP_mO7Vk5JtoN3fb0ahu44E0hO6ZKaRr/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0073.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rjZOAZ_8XEYbTCcuA9iy2013dDKjmdVH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0072.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZkP4zrheXRfWPm-Srmqoh2OUI_2Xq_CM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0071.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ffpz0lch5KBtBy1uuBSIX8M4wGiFpapD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0070.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Z71lnPawEv5dzQUUdrZc9YB95ouj3Mnl/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0069.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12e6A9mditaWvF89b80ExnO8tcYJAr_xs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0068.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RRpLmLHT36C63uoU37Yhtu5-Y8ADRYHL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0067.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_55nRCWaa2SH2Xz-DQ1smYb7yMnTyfQc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0066.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/189_KBcqXLMrlkRmPkqB8Z7Xl_PvW8A8V/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0064.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jCsgKLKFLLZEKWZQqDl1mLtJ4gKoNTHJ/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0063.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15nYyeBcoFrnC1Q0BE3GnJwGLuYurILvx/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0061.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/13bLibc-HbvbujWYAslcRhWySWXvocMDT/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0052.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1E_Hh1-cye8-koRmql1RgIw6gUeZ-5YII/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0051.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mUn_tL5X6ZhGI1PeZIE6ZP2JyKEJN62f/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0049.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1el3lIb1UJSpja3FIRKSKaUJlZxB-_x3p/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0048.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ecaxIfZzAcn892qk9tZafOUzdpc6No8e/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0046.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11HM9OPXOX0Y0JuXnjAcuu3ushBs9LrlN/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0045.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sU55zwv3rUUB7qJgEZJUwL9vkwNMtgmH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0041.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ivBKUAzxl7RMV0c0KIdW2djUHM80IKEs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0040.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UASge34DJwodtbgfcZBljtd2q9q_Y76V/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0038.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/149l94rhqyArpsLludbWQhQFqae1hPWbk/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0037.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DnV_FlB0SJUtL0kb_2yeDUMPzwHFtggo/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0035.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1BzALIZ4xj0B08gPfZBl8qlmEtfKCbol_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0034.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1x_v6zuRgROs0nTa8gXysVrwvHYkJzQvX/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0033.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZvJXIWA5e7bXyFNCiiqcOxZLMpueCCah/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0032.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QWPvQgsEM5UHo5G4imXw8ui2kjnJYnGG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0030.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1WAb77w3BlRSaFgKodNnV5HeqgQ_SlTVc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0029.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_caLcPwE6fjN1_cNFfyECm8pJr_kopxH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0027.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zirjKJ7RDb3T4xJQOMVpl33n2wI6LwmI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260221-WA0026.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1MV2DBYu-r1Lxy6KVc10c3wgziE0kzp1T/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0144.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1QaLeG9zxW3p5sMOStD77ie_P8UoqegmC/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0143.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1vSCNW4RXMvIGknVFfTrUva3Tyr5dvEh6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0139.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/171MyViIXo13P-21rpRVz1ormxig3ADWn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0138.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JqGPyAQo37YJwGgVuJbucHZpiyQw9kN0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0137.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1wRuQNjzQKgk1z9ymh4To2tPwXwVedAXE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0136.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1daRaaJ0EWEHJbGAydf2dKjsTtSEU1Ad_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0135.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JBCYBG-2WskV85hE18XqE_6e3sTvxDYN/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0134.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/16caDrT3cErEmTfxmypX-4InG2hNkN8hB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0133.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1-UmrXTZ89ZXK0hOANfJOImSZWQhPuV0k/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0132.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1A0qXBDKNiZKYjL1WaDenm8NgKdCH0BZa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0131.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Pv4FjYJ3BMZelal_huiBw7ie4AUMko_K/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0130.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19-py3DcYGII8A6r2xWpZeBJBrblQYO3P/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0129.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G80gkI7MwcqP9GB4qBqKqTcx05ube6F2/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0127.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1d6t7Okica08ZuV7wdkVrw52oDhgBf2zL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0126.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HNVAYOYYdx5VsMXd0MLSacrZAUXQ8wXM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0125.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V34KWvURgbJ70GZV_OWQghZwJblP7HAi/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0124.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/11clvlEMxU8_rsyDnVxUPVMcn31Mwkcmv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0123.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1xzXeNm5RUMdk-DagYxVfyd1IxI-jZd2Y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0122.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/170_6rR-sQZiGDcf8PXI4LWXB5XfVozCl/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0121.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1IL4tKfW58uFgTbnF1jzUILtTivplm0vc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0120.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OJKsriCD32pmSkTxF_gorJcSnZK_OAuw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0119.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1K_o3KlxVVo8zxnzUF7xSYkZz2lj9c4gR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0118.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1AoowKlwmnJfkz3Npi4a7JgND0wCc88nC/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0117.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1N4u_L2roiEfiZdsysc7kWBdyKRblZ7-y/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0116.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1sqowhzTrNekkrBUcG1ePZu7ikApNTGEp/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0115.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18jRYrhMZoqJRAQ3hUmx4kHdvYosWMaWP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0114.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1I9QfXvUZ1BI6NMT8T9bbGwSiWTnUvT82/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0113.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14FBxvrrkyb70dQNCTe-fj5HELGpI7B61/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0112.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1YDbXP863fOPWXIQfEtfRC7Fmj5c358Ds/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0111.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1134d4Pnmwdi4xl9fg-blnV66dXmKa9ro/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0110.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hugrrB1xiyqDmzu4FCYS5KAgAsf_E2CG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0109.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FmhN7RQt48pjcX6QPb6LiHaLhcfhZMHV/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0108.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/191MfvQ34gV4fQ51rFh20SZUwLOv8Tm2G/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0107.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cCUc7Hk-auZfiXSUBxaj91zqSY3hJvGa/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0106.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1VFYA3rjBmrLPOQwTrBRL4usqvd2gAUgM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0105.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bOtqsqAyyJ1U6sqEIsYz_P_Eon1bE-Ru/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0104.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18AsyaL-TEvGXl4KxF5CYaFLUqanYp7a7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0103.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mLalRwzFT_vt7OvfHvkl_bAACfOkrcHt/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0102.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V5AVBLZkGldy-aKiYNsEOidRaSEdEpaA/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0101.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UYLiQ9-PAVOq2WjEKo2dMshW4Z1DagpG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0100.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1fmeMMoxNg_j-S7WYluZpR_e3vyT-sFa_/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0099.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1C79joUR1_wfA0y5gREmYOT9TRdIwci5b/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0098.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1mgBabE8Kbt_qWs4kcaEbPdPMNUP1dFJ6/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0097.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1P1hzCjde-A9FIVWiaKZoCR5hnIHxAexd/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0096.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DOyv1LBoG3BHna5GThklgtArkVvz5Wz0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0095.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TnhY8X2oZVtWt4gucb1UzdFeu1t6tbto/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0093.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EgdHAoKbNEu_nDQT9bbwnnZK8mt48VK7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0092.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1txuUtFw9aXVQxKXr-oCUEKVun3E3y-sB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0091.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/124GkiWKnIWIX65iEVL9eYHmd5wqKRKDc/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0090.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1bMCULmOfpYD7dYpx4mwFKfLHqSiWNIHM/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0089.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1uK4RSdnydCReB6EVk0U5w8APvjnzd_Yf/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0085.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/113m9zu3_SQfnRacNhyILHTBmzHZJeWzR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0083.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ohwPyTVDQ_FGuA-EPKTWZPA9sfGMQvK5/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0081.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nuxksOVQQp_xGwejp2qa2BQV1KxvKjWL/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0080.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1NfbbJEedq8Rrw-nIE9lCnWlhFzGreIUs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0079.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1rQ-COwYhNmY0WpRy0BYJi48QtB3JC3TR/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0078.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_GlnxZ4X31hg2SDpIexkQ52WY5uk-df7/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0077.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1kwtScxexovV7C-xpz0OuBopW1_XH4aAB/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0076.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1hTu2OekOBLFa1f3odrsjyl982j8lIEVn/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0075.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iyw5nxQtlwCbGZaAFV_qu6wiav9iN1pG/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20260220-WA0074.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14GDUdxvhP6lWYxuKGdVP2-vNDJyuOP7H/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20251219-WA0038.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1P8UEwXgFj_Za6T5wH46UUgi5PDX9XM2g/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0066.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qOkTWHYq_Z7YD2yybTMSZokyXHjaUm8k/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0065.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Sw0bV-dHvs_KXnkKZ0U4SuMLJvK6BFX8/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0064.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1byBFoqG8TYNvRmX6qD4G1oRnWwvDkIAP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0062.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1n2sHMY5Ykpyf6g69soqtMzSSGOIdgLwU/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0061.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UgV9wmbKWPREkgWYSar26PT6It1iRBmy/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0060.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1T6jBhHnjGfyJsyHIeVS4DNdOwWDr4OQv/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250712-WA0059.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DZ-e4noIZYhOAD5Ha664KtJPZMhHnO2H/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250409-WA0025.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Og6mYVB9rAYaVTlxXmCSe34amtldUOoE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20250319-WA0004.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/14xOEW1mCgtKEY7kklyZwd8GS2HOrvMcw/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20241022-WA0033.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1FsoJe_I9U5bjSy5jXKkAuXLgQ5eCHxd0/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20241022-WA0031.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/19RsUH2aqGixUI2ALNk0vFfzFnA-fezJl/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20241022-WA0027.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_LJlhqXArmvDbkl4hqbKgVVuNcP53qAY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240924-WA0028.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ikGQU6a_6-Hi5WOiGc3AypnVpXd6XpRs/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240822-WA0028.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZaY0HwX4-AZ5t5WkgB7ruaG0fc0rHXIP/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240820-WA0035.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1OYat2tMeOjZueNN8TPXIZLFikLEMOeFY/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240417-WA0044.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17qQDybi6yV_x2ykJTwhj_ihdrnG2e4kH/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240308-WA0010.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JWoZhCwx60lsgd34ihq2FvfauSrcW3Ij/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240308-WA0006.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/156Oa0rpDJmunGvFjr5HrebEiv8nLEUMe/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20240308-WA0004.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1qDhodGG-phmf6V1cZotSwt18_LYg1-CI/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20231224-WA0090.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1zhW0gm5HCHnLibOXS9aQty4Yu8iGxiUE/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20231224-WA0085.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1m1I4JEqKBxqTMBAinHoHaFlEt58fID4X/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>IMG-20231223-WA0001.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1N06uPiC_YmeyL35tP1Rp70ywbYjBVfkz/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>image.jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1p7XXVZaIc9rbDs9kJXplCfZTeUzZZJ0N/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>image (4).jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1lTUhpwVAGRWLCaHj90WFu3OmDEisPyuD/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>image (3).jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/18J5j084BrA3f2uXnRRf5Rdeue4qZbWRu/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>image (2).jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1H6uGkRHy2diS4tTIliPlgg8uI0JaPbZb/view?usp=drivesdk</t>
+  </si>
+  <si>
+    <t>image (1).jpg</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1jwzvQWS43goC8Gmrp_SoW-rmW1U6lU8F/view?usp=drivesdk</t>
   </si>
   <si>
     <t>IMG-20260220-WA0029 - Rajesh Chintala.jpg</t>
@@ -263,7 +1313,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -278,6 +1328,15 @@
     <font>
       <u/>
       <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -294,7 +1353,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -303,6 +1362,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,6 +1914,1406 @@
         <v>81</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
@@ -891,7 +3356,182 @@
     <hyperlink r:id="rId38" ref="B39"/>
     <hyperlink r:id="rId39" ref="B40"/>
     <hyperlink r:id="rId40" ref="B41"/>
+    <hyperlink r:id="rId41" ref="B42"/>
+    <hyperlink r:id="rId42" ref="B43"/>
+    <hyperlink r:id="rId43" ref="B44"/>
+    <hyperlink r:id="rId44" ref="B45"/>
+    <hyperlink r:id="rId45" ref="B46"/>
+    <hyperlink r:id="rId46" ref="B47"/>
+    <hyperlink r:id="rId47" ref="B48"/>
+    <hyperlink r:id="rId48" ref="B49"/>
+    <hyperlink r:id="rId49" ref="B50"/>
+    <hyperlink r:id="rId50" ref="B51"/>
+    <hyperlink r:id="rId51" ref="B52"/>
+    <hyperlink r:id="rId52" ref="B53"/>
+    <hyperlink r:id="rId53" ref="B54"/>
+    <hyperlink r:id="rId54" ref="B55"/>
+    <hyperlink r:id="rId55" ref="B56"/>
+    <hyperlink r:id="rId56" ref="B57"/>
+    <hyperlink r:id="rId57" ref="B58"/>
+    <hyperlink r:id="rId58" ref="B59"/>
+    <hyperlink r:id="rId59" ref="B60"/>
+    <hyperlink r:id="rId60" ref="B61"/>
+    <hyperlink r:id="rId61" ref="B62"/>
+    <hyperlink r:id="rId62" ref="B63"/>
+    <hyperlink r:id="rId63" ref="B64"/>
+    <hyperlink r:id="rId64" ref="B65"/>
+    <hyperlink r:id="rId65" ref="B66"/>
+    <hyperlink r:id="rId66" ref="B67"/>
+    <hyperlink r:id="rId67" ref="B68"/>
+    <hyperlink r:id="rId68" ref="B69"/>
+    <hyperlink r:id="rId69" ref="B70"/>
+    <hyperlink r:id="rId70" ref="B71"/>
+    <hyperlink r:id="rId71" ref="B72"/>
+    <hyperlink r:id="rId72" ref="B73"/>
+    <hyperlink r:id="rId73" ref="B74"/>
+    <hyperlink r:id="rId74" ref="B75"/>
+    <hyperlink r:id="rId75" ref="B76"/>
+    <hyperlink r:id="rId76" ref="B77"/>
+    <hyperlink r:id="rId77" ref="B78"/>
+    <hyperlink r:id="rId78" ref="B79"/>
+    <hyperlink r:id="rId79" ref="B80"/>
+    <hyperlink r:id="rId80" ref="B81"/>
+    <hyperlink r:id="rId81" ref="B82"/>
+    <hyperlink r:id="rId82" ref="B83"/>
+    <hyperlink r:id="rId83" ref="B84"/>
+    <hyperlink r:id="rId84" ref="B85"/>
+    <hyperlink r:id="rId85" ref="B86"/>
+    <hyperlink r:id="rId86" ref="B87"/>
+    <hyperlink r:id="rId87" ref="B88"/>
+    <hyperlink r:id="rId88" ref="B89"/>
+    <hyperlink r:id="rId89" ref="B90"/>
+    <hyperlink r:id="rId90" ref="B91"/>
+    <hyperlink r:id="rId91" ref="B92"/>
+    <hyperlink r:id="rId92" ref="B93"/>
+    <hyperlink r:id="rId93" ref="B94"/>
+    <hyperlink r:id="rId94" ref="B95"/>
+    <hyperlink r:id="rId95" ref="B96"/>
+    <hyperlink r:id="rId96" ref="B97"/>
+    <hyperlink r:id="rId97" ref="B98"/>
+    <hyperlink r:id="rId98" ref="B99"/>
+    <hyperlink r:id="rId99" ref="B100"/>
+    <hyperlink r:id="rId100" ref="B101"/>
+    <hyperlink r:id="rId101" ref="B102"/>
+    <hyperlink r:id="rId102" ref="B103"/>
+    <hyperlink r:id="rId103" ref="B104"/>
+    <hyperlink r:id="rId104" ref="B105"/>
+    <hyperlink r:id="rId105" ref="B106"/>
+    <hyperlink r:id="rId106" ref="B107"/>
+    <hyperlink r:id="rId107" ref="B108"/>
+    <hyperlink r:id="rId108" ref="B109"/>
+    <hyperlink r:id="rId109" ref="B110"/>
+    <hyperlink r:id="rId110" ref="B111"/>
+    <hyperlink r:id="rId111" ref="B112"/>
+    <hyperlink r:id="rId112" ref="B113"/>
+    <hyperlink r:id="rId113" ref="B114"/>
+    <hyperlink r:id="rId114" ref="B115"/>
+    <hyperlink r:id="rId115" ref="B116"/>
+    <hyperlink r:id="rId116" ref="B117"/>
+    <hyperlink r:id="rId117" ref="B118"/>
+    <hyperlink r:id="rId118" ref="B119"/>
+    <hyperlink r:id="rId119" ref="B120"/>
+    <hyperlink r:id="rId120" ref="B121"/>
+    <hyperlink r:id="rId121" ref="B122"/>
+    <hyperlink r:id="rId122" ref="B123"/>
+    <hyperlink r:id="rId123" ref="B124"/>
+    <hyperlink r:id="rId124" ref="B125"/>
+    <hyperlink r:id="rId125" ref="B126"/>
+    <hyperlink r:id="rId126" ref="B127"/>
+    <hyperlink r:id="rId127" ref="B128"/>
+    <hyperlink r:id="rId128" ref="B129"/>
+    <hyperlink r:id="rId129" ref="B130"/>
+    <hyperlink r:id="rId130" ref="B131"/>
+    <hyperlink r:id="rId131" ref="B132"/>
+    <hyperlink r:id="rId132" ref="B133"/>
+    <hyperlink r:id="rId133" ref="B134"/>
+    <hyperlink r:id="rId134" ref="B135"/>
+    <hyperlink r:id="rId135" ref="B136"/>
+    <hyperlink r:id="rId136" ref="B137"/>
+    <hyperlink r:id="rId137" ref="B138"/>
+    <hyperlink r:id="rId138" ref="B139"/>
+    <hyperlink r:id="rId139" ref="B140"/>
+    <hyperlink r:id="rId140" ref="B141"/>
+    <hyperlink r:id="rId141" ref="B142"/>
+    <hyperlink r:id="rId142" ref="B143"/>
+    <hyperlink r:id="rId143" ref="B144"/>
+    <hyperlink r:id="rId144" ref="B145"/>
+    <hyperlink r:id="rId145" ref="B146"/>
+    <hyperlink r:id="rId146" ref="B147"/>
+    <hyperlink r:id="rId147" ref="B148"/>
+    <hyperlink r:id="rId148" ref="B149"/>
+    <hyperlink r:id="rId149" ref="B150"/>
+    <hyperlink r:id="rId150" ref="B151"/>
+    <hyperlink r:id="rId151" ref="B152"/>
+    <hyperlink r:id="rId152" ref="B153"/>
+    <hyperlink r:id="rId153" ref="B154"/>
+    <hyperlink r:id="rId154" ref="B155"/>
+    <hyperlink r:id="rId155" ref="B156"/>
+    <hyperlink r:id="rId156" ref="B157"/>
+    <hyperlink r:id="rId157" ref="B158"/>
+    <hyperlink r:id="rId158" ref="B159"/>
+    <hyperlink r:id="rId159" ref="B160"/>
+    <hyperlink r:id="rId160" ref="B161"/>
+    <hyperlink r:id="rId161" ref="B162"/>
+    <hyperlink r:id="rId162" ref="B163"/>
+    <hyperlink r:id="rId163" ref="B164"/>
+    <hyperlink r:id="rId164" ref="B165"/>
+    <hyperlink r:id="rId165" ref="B166"/>
+    <hyperlink r:id="rId166" ref="B167"/>
+    <hyperlink r:id="rId167" ref="B168"/>
+    <hyperlink r:id="rId168" ref="B169"/>
+    <hyperlink r:id="rId169" ref="B170"/>
+    <hyperlink r:id="rId170" ref="B171"/>
+    <hyperlink r:id="rId171" ref="B172"/>
+    <hyperlink r:id="rId172" ref="B173"/>
+    <hyperlink r:id="rId173" ref="B174"/>
+    <hyperlink r:id="rId174" ref="B175"/>
+    <hyperlink r:id="rId175" ref="B176"/>
+    <hyperlink r:id="rId176" ref="B177"/>
+    <hyperlink r:id="rId177" ref="B178"/>
+    <hyperlink r:id="rId178" ref="B179"/>
+    <hyperlink r:id="rId179" ref="B180"/>
+    <hyperlink r:id="rId180" ref="B181"/>
+    <hyperlink r:id="rId181" ref="B182"/>
+    <hyperlink r:id="rId182" ref="B183"/>
+    <hyperlink r:id="rId183" ref="B184"/>
+    <hyperlink r:id="rId184" ref="B185"/>
+    <hyperlink r:id="rId185" ref="B186"/>
+    <hyperlink r:id="rId186" ref="B187"/>
+    <hyperlink r:id="rId187" ref="B188"/>
+    <hyperlink r:id="rId188" ref="B189"/>
+    <hyperlink r:id="rId189" ref="B190"/>
+    <hyperlink r:id="rId190" ref="B191"/>
+    <hyperlink r:id="rId191" ref="B192"/>
+    <hyperlink r:id="rId192" ref="B193"/>
+    <hyperlink r:id="rId193" ref="B194"/>
+    <hyperlink r:id="rId194" ref="B195"/>
+    <hyperlink r:id="rId195" ref="B196"/>
+    <hyperlink r:id="rId196" ref="B197"/>
+    <hyperlink r:id="rId197" ref="B198"/>
+    <hyperlink r:id="rId198" ref="B199"/>
+    <hyperlink r:id="rId199" ref="B200"/>
+    <hyperlink r:id="rId200" ref="B201"/>
+    <hyperlink r:id="rId201" ref="B202"/>
+    <hyperlink r:id="rId202" ref="B203"/>
+    <hyperlink r:id="rId203" ref="B204"/>
+    <hyperlink r:id="rId204" ref="B205"/>
+    <hyperlink r:id="rId205" ref="B206"/>
+    <hyperlink r:id="rId206" ref="B207"/>
+    <hyperlink r:id="rId207" ref="B208"/>
+    <hyperlink r:id="rId208" ref="B209"/>
+    <hyperlink r:id="rId209" ref="B210"/>
+    <hyperlink r:id="rId210" ref="B211"/>
+    <hyperlink r:id="rId211" ref="B212"/>
+    <hyperlink r:id="rId212" ref="B213"/>
+    <hyperlink r:id="rId213" ref="B214"/>
+    <hyperlink r:id="rId214" ref="B215"/>
+    <hyperlink r:id="rId215" ref="B216"/>
   </hyperlinks>
-  <drawing r:id="rId41"/>
+  <drawing r:id="rId216"/>
 </worksheet>
 </file>